--- a/工作-大圣牌/战棋/部将表.xlsx
+++ b/工作-大圣牌/战棋/部将表.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\Notes\工作-大圣牌\战棋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B61366DE-D6CE-4004-B6B3-A943D306BB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711E6245-68F1-4E54-ACFE-46A49B4F5E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
   <si>
     <t>等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -81,10 +82,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>出售：获得一张普通蛛丝(使一个部将+1 +1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大网蛛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -97,6 +94,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>2/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>每当你释放法术时，获得+1+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -133,10 +134,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合更始：获得一张普通蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>登场:对商店中的部将释放一次普通蛛丝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -182,6 +179,110 @@
   </si>
   <si>
     <t>登场：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出售：获得一张蛛丝(使一个部将+1 +1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登场：获得一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合更始：获得一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金丝银丝普通蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野猪人like</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每当你花费8个金币，获得一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的蛛丝会释放两次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放三次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外两张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当部署盘丝洞部将到部署区时，获得一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>永久获得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结网：有额外的一张蛛丝施加给另外一个盘丝洞部将</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结网：当回合获得护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后援：对其他盘丝洞部将释放一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放两次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残念：召唤两个小蜘蛛并对他们释放一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亡语: 使蛛丝额外给予+1攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登场：使蛛丝额外给予+1生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>业报(3):使蛛丝额外给予+1生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抉择1：获得三张蛛丝；抉择2：使蛛丝额外给予+1/+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合更始：你的蛛丝额外+1/+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残念：对其他盘丝洞部将释放三张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复两次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变为+2/+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2/5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -228,12 +329,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E19F982C-7D94-4D1E-A263-41722DE2E3B1}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="9" style="1"/>
@@ -593,7 +697,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -607,7 +711,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -618,13 +722,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -635,7 +739,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>17</v>
@@ -655,7 +759,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -666,10 +770,10 @@
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -677,10 +781,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -688,7 +792,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
@@ -720,7 +824,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -738,10 +842,10 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
         <v>26</v>
-      </c>
-      <c r="E16" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -749,7 +853,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -760,10 +864,15 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" t="s">
         <v>34</v>
       </c>
-      <c r="E18" t="s">
-        <v>35</v>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -771,4 +880,255 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{680D7D93-5AE3-4DC8-9319-D55788C423FC}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="45.125" customWidth="1"/>
+    <col min="5" max="5" width="18.375" customWidth="1"/>
+    <col min="7" max="7" width="11.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D23" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/工作-大圣牌/战棋/部将表.xlsx
+++ b/工作-大圣牌/战棋/部将表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\Notes\工作-大圣牌\战棋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711E6245-68F1-4E54-ACFE-46A49B4F5E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E45CBB-33B9-48C1-B7C8-3E6143CBB336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
   <si>
     <t>等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -226,10 +226,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>结网：有额外的一张蛛丝施加给另外一个盘丝洞部将</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>结网：当回合获得护盾</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -283,6 +279,26 @@
   </si>
   <si>
     <t>2/5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后援：获得两张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾，当友方部将失去护盾时，获得一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾，结网(1)：有额外的一张蛛丝施加给另外一个盘丝洞部将</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结网(3):吞噬商店中的一个部将</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -954,7 +970,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>46</v>
@@ -965,10 +981,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -979,7 +995,7 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1003,17 +1019,22 @@
       <c r="A8">
         <v>3</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -1021,12 +1042,18 @@
         <v>3</v>
       </c>
       <c r="C10" s="1"/>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1"/>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -1034,28 +1061,31 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>4</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="2" t="s">
-        <v>47</v>
+      <c r="D14" t="s">
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -1064,10 +1094,7 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1088,10 +1115,10 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" t="s">
         <v>57</v>
-      </c>
-      <c r="E17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1112,10 +1139,10 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
         <v>49</v>
-      </c>
-      <c r="E19" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">

--- a/工作-大圣牌/战棋/部将表.xlsx
+++ b/工作-大圣牌/战棋/部将表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\Notes\工作-大圣牌\战棋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E45CBB-33B9-48C1-B7C8-3E6143CBB336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFD1E71-58FF-4B47-89EB-BB28DFB67FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="72">
   <si>
     <t>等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -202,10 +202,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每当你花费8个金币，获得一张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>你的蛛丝会释放两次</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -299,6 +295,34 @@
   </si>
   <si>
     <t>结网(3):吞噬商店中的一个部将</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每当你花费7个金币，获得一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得双倍身材</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -970,10 +994,10 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -981,10 +1005,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -995,7 +1019,7 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1009,7 +1033,7 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -1020,10 +1044,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -1031,10 +1055,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -1043,7 +1067,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1052,7 +1076,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -1061,7 +1085,7 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1070,64 +1094,77 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>5</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>5</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="s">
         <v>42</v>
-      </c>
-      <c r="E16" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>5</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="D17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" t="s">
         <v>56</v>
-      </c>
-      <c r="E17" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>6</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -1137,12 +1174,14 @@
       <c r="A19">
         <v>6</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" t="s">
         <v>48</v>
-      </c>
-      <c r="E19" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">

--- a/工作-大圣牌/战棋/部将表.xlsx
+++ b/工作-大圣牌/战棋/部将表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\Notes\工作-大圣牌\战棋\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\Obsidian Vault\工作-大圣牌\战棋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E45CBB-33B9-48C1-B7C8-3E6143CBB336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E2E8E7-9754-405C-9FDE-DAC934669279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="118">
   <si>
     <t>等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,211 +94,359 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>每当你释放法术时，获得+1+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>守网蛛妖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>业报(3)：获得一张普通蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得一张银丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小蛛妖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>衍生牌(关联)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登场:对商店中的部将释放一次普通蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后援：对其他盘丝洞部将释放一次普通蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放银丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每当你花费8个金币，获得一张普通蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小蜘蛛：1/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后援：获得1金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残念:召唤两个小蜘蛛并对他们释放一次普通蛛丝并获得护法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残念：你的蛛丝额外获得+1/+1的加成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改为+2/+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登场：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出售：获得一张蛛丝(使一个部将+1 +1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登场：获得一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合更始：获得一张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金丝银丝普通蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>部将名称</t>
+  </si>
+  <si>
+    <t>身材</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>金色版本</t>
+  </si>
+  <si>
+    <t>美术需求</t>
+  </si>
+  <si>
+    <t>衍生牌(关联)</t>
+  </si>
+  <si>
+    <t>蜘蛛卵</t>
+  </si>
+  <si>
+    <t>1/3</t>
+  </si>
+  <si>
+    <t>出售：获得一张蛛丝(使一个部将+1 +1)</t>
+  </si>
+  <si>
+    <t>小蛛妖</t>
+  </si>
+  <si>
+    <t>2/1</t>
+  </si>
+  <si>
+    <t>登场：获得一张蛛丝</t>
+  </si>
+  <si>
+    <t>获得两张</t>
+  </si>
+  <si>
+    <t>护网小妖</t>
+  </si>
+  <si>
+    <t>3/3</t>
+  </si>
+  <si>
+    <t>结网：当回合获得护盾</t>
+  </si>
+  <si>
+    <t>永久获得</t>
+  </si>
+  <si>
+    <t>盘丝侍女</t>
+  </si>
+  <si>
+    <t>2/5</t>
+  </si>
+  <si>
+    <t>登场：使蛛丝额外给予+1生命</t>
+  </si>
+  <si>
+    <t>蛛卵小妖</t>
+  </si>
+  <si>
     <t>2/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每当你释放法术时，获得+1+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>守网蛛妖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3/3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残念：召唤两个小蜘蛛并对他们释放一张蛛丝</t>
+  </si>
+  <si>
+    <t>小蜘蛛：1/1</t>
+  </si>
+  <si>
+    <t>巡洞蛛妖</t>
   </si>
   <si>
     <t>3/4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业报(3)：获得一张普通蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得一张银丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小蛛妖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>衍生牌(关联)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登场:对商店中的部将释放一次普通蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>后援：对其他盘丝洞部将释放一次普通蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放银丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每当你花费8个金币，获得一张普通蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小蜘蛛：1/1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4/5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4/3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>后援：获得1金币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>残念:召唤两个小蜘蛛并对他们释放一次普通蛛丝并获得护法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>残念：你的蛛丝额外获得+1/+1的加成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>改为+2/+2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登场：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出售：获得一张蛛丝(使一个部将+1 +1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登场：获得一张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合更始：获得一张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金丝银丝普通蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>野猪人like</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当部署盘丝洞部将到部署区时，获得一张蛛丝</t>
+  </si>
+  <si>
+    <t>护网蛛将</t>
+  </si>
+  <si>
+    <t>3/5</t>
+  </si>
+  <si>
+    <t>护盾，当友方部将失去护盾时，获得一张蛛丝</t>
+  </si>
+  <si>
+    <t>毒丝妖女</t>
+  </si>
+  <si>
+    <t>5/1</t>
+  </si>
+  <si>
+    <t>亡语: 使蛛丝额外给予+1攻击</t>
+  </si>
+  <si>
+    <t>濯垢侍女</t>
+  </si>
+  <si>
+    <t>后援：获得两张蛛丝</t>
+  </si>
+  <si>
+    <t>盘丝妖姬</t>
+  </si>
+  <si>
+    <t>抉择1：获得三张蛛丝；抉择2：使蛛丝额外给予+1/+1</t>
+  </si>
+  <si>
+    <t>黄花蛛女</t>
+  </si>
+  <si>
+    <t>业报(3):使蛛丝额外给予+1生命</t>
+  </si>
+  <si>
+    <t>牵丝蛛母</t>
+  </si>
+  <si>
+    <t>护盾，结网(1)：有额外的一张蛛丝施加给另外一个盘丝洞部将</t>
+  </si>
+  <si>
+    <t>额外两张蛛丝</t>
+  </si>
+  <si>
+    <t>盘丝夫人</t>
+  </si>
+  <si>
+    <t>回合更始：你的蛛丝额外+1/+1</t>
+  </si>
+  <si>
+    <t>变为+2/+2</t>
+  </si>
+  <si>
+    <t>吞金蛛母</t>
+  </si>
+  <si>
+    <t>结网(3):吞噬商店中的一个部将</t>
+  </si>
+  <si>
+    <t>千丝娘娘</t>
+  </si>
+  <si>
+    <t>你的蛛丝会释放两次</t>
+  </si>
+  <si>
+    <t>释放三次</t>
+  </si>
+  <si>
+    <t>抱卵蛛母</t>
+  </si>
+  <si>
+    <t>残念：对其他盘丝洞部将释放三张蛛丝</t>
+  </si>
+  <si>
+    <t>重复两次</t>
+  </si>
+  <si>
+    <t>百眼魔君</t>
   </si>
   <si>
     <t>每当你花费8个金币，获得一张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的蛛丝会释放两次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放三次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外两张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当部署盘丝洞部将到部署区时，获得一张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>永久获得</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结网：当回合获得护盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>七蛛夫人</t>
   </si>
   <si>
     <t>后援：对其他盘丝洞部将释放一张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>释放两次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>残念：召唤两个小蜘蛛并对他们释放一张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亡语: 使蛛丝额外给予+1攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登场：使蛛丝额外给予+1生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业报(3):使蛛丝额外给予+1生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抉择1：获得三张蛛丝；抉择2：使蛛丝额外给予+1/+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合更始：你的蛛丝额外+1/+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>残念：对其他盘丝洞部将释放三张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复两次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>变为+2/+2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5/1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2/5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>后援：获得两张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>护盾，当友方部将失去护盾时，获得一张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3/5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>护盾，结网(1)：有额外的一张蛛丝施加给另外一个盘丝洞部将</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结网(3):吞噬商店中的一个部将</t>
+  </si>
+  <si>
+    <t>卡面简述</t>
+  </si>
+  <si>
+    <t>出售获得蛛丝</t>
+  </si>
+  <si>
+    <t>登场获得蛛丝</t>
+  </si>
+  <si>
+    <t>结网获得护盾</t>
+  </si>
+  <si>
+    <t>增强蛛丝生命</t>
+  </si>
+  <si>
+    <t>残念唤蛛施丝</t>
+  </si>
+  <si>
+    <t>部署获得蛛丝</t>
+  </si>
+  <si>
+    <t>失盾获得蛛丝</t>
+  </si>
+  <si>
+    <t>阵亡增强蛛丝</t>
+  </si>
+  <si>
+    <t>后援获得蛛丝</t>
+  </si>
+  <si>
+    <t>抉择蛛丝强化</t>
+  </si>
+  <si>
+    <t>业报增强生命</t>
+  </si>
+  <si>
+    <t>结网传递蛛丝</t>
+  </si>
+  <si>
+    <t>回合增强蛛丝</t>
+  </si>
+  <si>
+    <t>结网吞噬部将</t>
+  </si>
+  <si>
+    <t>蛛丝释放两次</t>
+  </si>
+  <si>
+    <t>残念群施蛛丝</t>
+  </si>
+  <si>
+    <t>花钱获得蛛丝</t>
+  </si>
+  <si>
+    <t>盘丝核心</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>野猪人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>like</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -306,7 +454,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,13 +470,46 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6D4C41"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -345,14 +526,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -373,9 +566,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -413,7 +606,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -519,7 +712,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -661,7 +854,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -670,16 +863,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E19F982C-7D94-4D1E-A263-41722DE2E3B1}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9" style="1"/>
     <col min="4" max="4" width="61" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
-    <col min="7" max="7" width="12.125" customWidth="1"/>
+    <col min="6" max="6" width="11.58203125" customWidth="1"/>
+    <col min="7" max="7" width="12.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,10 +892,10 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -713,27 +906,27 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -744,13 +937,13 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -758,137 +951,137 @@
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
         <v>19</v>
       </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>6</v>
       </c>
       <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
         <v>25</v>
       </c>
-      <c r="E16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>6</v>
       </c>
       <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
         <v>33</v>
       </c>
-      <c r="E18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -900,258 +1093,415 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{680D7D93-5AE3-4DC8-9319-D55788C423FC}">
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="45.125" customWidth="1"/>
-    <col min="5" max="5" width="18.375" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="4" max="4" width="45.08203125" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.08203125" customWidth="1"/>
+    <col min="8" max="8" width="16.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:8" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>4</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>5</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>6</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>5</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18">
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
         <v>6</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>6</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D23" s="1"/>
     </row>
   </sheetData>

--- a/工作-大圣牌/战棋/部将表.xlsx
+++ b/工作-大圣牌/战棋/部将表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\Notes\工作-大圣牌\战棋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E37BC16-B634-4196-8CFA-F697B0A150B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2279A9D8-8AB6-4808-8941-31F85E4A67B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
   </bookViews>
   <sheets>
     <sheet name="盘丝洞1-额外关键词" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="296">
   <si>
     <t>蜘蛛卵</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,9 +90,6 @@
     <t>2/1</t>
   </si>
   <si>
-    <t>3/3</t>
-  </si>
-  <si>
     <t>2/5</t>
   </si>
   <si>
@@ -285,9 +282,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5/6</t>
-  </si>
-  <si>
     <t>5/8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -542,9 +536,6 @@
   </si>
   <si>
     <t>2/4</t>
-  </si>
-  <si>
-    <t>2/4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -811,9 +802,6 @@
   </si>
   <si>
     <t>蛛巢</t>
-  </si>
-  <si>
-    <t>蛛巢</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -847,328 +835,325 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>小蜘蛛卵</t>
+  </si>
+  <si>
+    <t>地府蜘蛛</t>
+  </si>
+  <si>
+    <t>贪财蛛妖</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>使一个友方部将获得+1/+1。</t>
+  </si>
+  <si>
+    <t>产卵/经济</t>
+  </si>
+  <si>
+    <t>盘丝洞/地府</t>
+  </si>
+  <si>
+    <t>转生。</t>
+  </si>
+  <si>
+    <t>4/2，转生。</t>
+  </si>
+  <si>
+    <t>嗜血：获得+1生命值。</t>
+  </si>
+  <si>
+    <t>6/4，嗜血：获得+2生命值。</t>
+  </si>
+  <si>
+    <t>大网蛛</t>
+  </si>
+  <si>
+    <t>缠丝蛛女</t>
+  </si>
+  <si>
+    <t>守网蛛妖</t>
+  </si>
+  <si>
+    <t>左侧相邻部将获得：嗜血：获得+1攻击力。</t>
+  </si>
+  <si>
+    <t>4/6，后援：本局中，属性增强类神通给予的属性额外+2生命值。</t>
+  </si>
+  <si>
+    <t>6/4，后援：本局中，属性增强类神通给予的属性额外+2攻击力。</t>
+  </si>
+  <si>
+    <t>嗜血：获取1张香火钱。</t>
+  </si>
+  <si>
+    <t>织巢蛛妖</t>
+  </si>
+  <si>
+    <t>毒丝侍女</t>
+  </si>
+  <si>
+    <t>饮血蛛将</t>
+  </si>
+  <si>
+    <t>嗜血成长</t>
+  </si>
+  <si>
+    <t>嗜血：其他友方部将永久获得+1/+1。</t>
+  </si>
+  <si>
+    <t>12/12，嗜血：其他友方部将永久获得+2/+2。</t>
+  </si>
+  <si>
+    <t>6/12，业报（4）：获得两张蜘蛛蛋。</t>
+  </si>
+  <si>
+    <t>牵丝蛛姬</t>
+  </si>
+  <si>
+    <t>嗜血/触发</t>
+  </si>
+  <si>
+    <t>先手：触发1次左侧相邻部将的嗜血。</t>
+  </si>
+  <si>
+    <t>检索/体系补强</t>
+  </si>
+  <si>
+    <t>登场：如果部署区有其他盘丝洞部将，探寻1张盘丝洞势力的部将，不超过当前等级。</t>
+  </si>
+  <si>
+    <t>蛛卵守巢者</t>
+  </si>
+  <si>
+    <t>产卵/亡语铺场</t>
+  </si>
+  <si>
+    <t>血网妖女</t>
+  </si>
+  <si>
+    <t>嗜血核心</t>
+  </si>
+  <si>
+    <t>你的嗜血效果会触发两次。</t>
+  </si>
+  <si>
+    <t>8/14，你的嗜血效果会触发三次。</t>
+  </si>
+  <si>
+    <t>神通/产卵核心</t>
+  </si>
+  <si>
+    <t>7/7</t>
+  </si>
+  <si>
+    <t>使用后随机获得一张蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每当你获得一张手牌，使一个友方盘丝洞部将获得+1/+1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/8，先手：触发1次相邻部将的嗜血。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产卵终端</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗜血终端</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合更使：本局中，属性增强类神通给予的属性额外+1生命值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合更使：本局中，属性增强类神通给予的属性额外+1攻击力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/20，释放两次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整军备战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使所有部将获得+1/+1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在友方攻击时施加一个整军备战法术。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/10，鼓舞：获得2张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼓舞：获得1张蛛丝。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>业报（4）：获得1张蜘蛛蛋。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/6，残念：对随机一个敌方部将造成6点法术伤害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀敌方单位后触发对应效果(即使击杀敌方部将后死亡也会触发)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残念：对随机一个敌方部将造成3点法术伤害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猛毒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/4，猛毒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄胎蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>碧青蛛卵</t>
-  </si>
-  <si>
-    <t>小蜘蛛卵</t>
-  </si>
-  <si>
-    <t>地府蜘蛛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤纹蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗜血：使其他盘丝洞部将获得+1/+1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>金壳蛛卵</t>
-  </si>
-  <si>
-    <t>赤纹蛛卵</t>
-  </si>
-  <si>
-    <t>玄胎蛛卵</t>
-  </si>
-  <si>
-    <t>贪财蛛妖</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>神通/产卵</t>
-  </si>
-  <si>
-    <t>使一个友方部将获得+1/+1。</t>
-  </si>
-  <si>
-    <t>产卵/经济</t>
-  </si>
-  <si>
-    <t>香火钱</t>
-  </si>
-  <si>
-    <t>经济牌</t>
-  </si>
-  <si>
-    <t>通用</t>
-  </si>
-  <si>
-    <t>经济</t>
-  </si>
-  <si>
-    <t>使用后获得1金币。</t>
-  </si>
-  <si>
-    <t>盘丝洞/地府</t>
-  </si>
-  <si>
-    <t>产卵/转生</t>
-  </si>
-  <si>
-    <t>转生。</t>
-  </si>
-  <si>
-    <t>4/2，转生。</t>
-  </si>
-  <si>
-    <t>嗜血：获得+1生命值。</t>
-  </si>
-  <si>
-    <t>6/4，嗜血：获得+2生命值。</t>
-  </si>
-  <si>
-    <t>大网蛛</t>
-  </si>
-  <si>
-    <t>产卵/法伤</t>
-  </si>
-  <si>
-    <t>残念：对随机一个敌方部将造成3点法术伤害。</t>
-  </si>
-  <si>
-    <t>缠丝蛛女</t>
-  </si>
-  <si>
-    <t>神通成长</t>
-  </si>
-  <si>
-    <t>每当你释放神通时，获得+1/+1。</t>
-  </si>
-  <si>
-    <t>6/6，每当你释放神通时，获得+2/+2。</t>
-  </si>
-  <si>
-    <t>守网蛛妖</t>
-  </si>
-  <si>
-    <t>嗜血辅助</t>
-  </si>
-  <si>
-    <t>左侧相邻部将获得：嗜血：获得+1攻击力。</t>
-  </si>
-  <si>
-    <t>6/8，左侧相邻部将获得：嗜血：获得+2攻击力。</t>
-  </si>
-  <si>
-    <t>残念：召唤1个小蛛妖。</t>
-  </si>
-  <si>
-    <t>6/4，残念：召唤2个小蛛妖。</t>
-  </si>
-  <si>
-    <t>产卵/神通强化</t>
-  </si>
-  <si>
-    <t>4/6，后援：本局中，属性增强类神通给予的属性额外+2生命值。</t>
-  </si>
-  <si>
-    <t>产卵/群体成长</t>
-  </si>
-  <si>
-    <t>登场：使其他盘丝洞部将获得+1/+1。</t>
-  </si>
-  <si>
-    <t>4/8，登场：使其他盘丝洞部将获得+2/+2。</t>
-  </si>
-  <si>
-    <t>6/4，后援：本局中，属性增强类神通给予的属性额外+2攻击力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/4，嗜血：使其他盘丝洞部将获得+2/+2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/8，嗜血：获取2张香火钱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6/2，每当你获得一张手牌，使一个友方盘丝洞部将获得+2/+2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>频率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗜血/灵力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神通强化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>嗜血/经济</t>
-  </si>
-  <si>
-    <t>嗜血：获取1张香火钱。</t>
-  </si>
-  <si>
-    <t>10/8，嗜血：获取2张香火钱。</t>
-  </si>
-  <si>
-    <t>出售：额外获得1金币。</t>
-  </si>
-  <si>
-    <t>4/4，出售：额外获得2金币。</t>
-  </si>
-  <si>
-    <t>织巢蛛妖</t>
-  </si>
-  <si>
-    <t>产卵/成长</t>
-  </si>
-  <si>
-    <t>6/10，每当你获得一张蜘蛛蛋，使一个友方盘丝洞部将获得+2/+2。</t>
-  </si>
-  <si>
-    <t>毒丝侍女</t>
-  </si>
-  <si>
-    <t>饮血蛛将</t>
-  </si>
-  <si>
-    <t>嗜血成长</t>
-  </si>
-  <si>
-    <t>嗜血：其他友方部将永久获得+1/+1。</t>
-  </si>
-  <si>
-    <t>12/12，嗜血：其他友方部将永久获得+2/+2。</t>
-  </si>
-  <si>
-    <t>6/12，业报（4）：获得两张蜘蛛蛋。</t>
-  </si>
-  <si>
-    <t>牵丝蛛姬</t>
-  </si>
-  <si>
-    <t>嗜血/触发</t>
-  </si>
-  <si>
-    <t>先手：触发1次左侧相邻部将的嗜血。</t>
-  </si>
-  <si>
-    <t>检索/体系补强</t>
-  </si>
-  <si>
-    <t>登场：如果部署区有其他盘丝洞部将，探寻1张盘丝洞势力的部将，不超过当前等级。</t>
-  </si>
-  <si>
-    <t>10/12，登场：如果部署区有其他盘丝洞部将，探寻2张盘丝洞势力的部将，不超过当前等级。</t>
-  </si>
-  <si>
-    <t>蛛卵守巢者</t>
-  </si>
-  <si>
-    <t>产卵/亡语铺场</t>
-  </si>
-  <si>
-    <t>10/10，残念：召唤四个大网蛛。</t>
-  </si>
-  <si>
-    <t>血网妖女</t>
-  </si>
-  <si>
-    <t>嗜血核心</t>
-  </si>
-  <si>
-    <t>你的嗜血效果会触发两次。</t>
-  </si>
-  <si>
-    <t>8/14，你的嗜血效果会触发三次。</t>
-  </si>
-  <si>
-    <t>神通/产卵核心</t>
-  </si>
-  <si>
-    <t>7/7</t>
-  </si>
-  <si>
-    <t>14/14，嗜血：获得+4/+4。你的嗜血效果改为对所有拥有嗜血的友方部将生效。</t>
-  </si>
-  <si>
-    <t>使用后随机获得一张蛛卵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2/2，衍生部将</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大金砖，使用后获得2金币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>后援：获得一张蜘蛛蛋。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每当你获得一张手牌，使一个友方盘丝洞部将获得+1/+1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8/8，先手：触发1次相邻部将的嗜血。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每当对己方使用属性增强类神通时，额外对一个随机友方盘丝洞部将施放一次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产卵终端</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗜血终端</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3/1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合更使：本局中，属性增强类神通给予的属性额外+1生命值。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合更使：本局中，属性增强类神通给予的属性额外+1攻击力。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10/20，释放两次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>整军备战</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使所有部将获得+1/+1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在友方攻击时施加一个整军备战法术。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗜血：获得+2/+2。你的嗜血效果全部友方部将共享。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4/4，后援：获得两张蜘蛛蛋。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产卵/铺场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4/10，鼓舞：获得2张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鼓舞：获得1张蛛丝。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业报（4）：获得1张蜘蛛蛋。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>残念：召唤2个大网蛛。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12/18，每当你使用属性增强类神通时，额外对两个随机友方盘丝洞部将施放一次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4/6，残念：对随机一个敌方部将造成6点法术伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀敌方单位后触发对应效果(即使击杀敌方部将后死亡也会触发)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒转</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中期战力提升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中期战力提升，也是获取蛛丝的来源之一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破碎蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/4，登场：获得2张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6/4，登场：如果部署区有其他盘丝洞部将，探寻2张盘丝洞势力的部将，不超过当前等级。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残念：召唤2个大网蛛，其继承灵力加成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/10，残念：召唤四个大网蛛，其继承灵力加成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂怒，嗜血：获得+1/+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗜血：友方部将获得+2/+2。你的嗜血效果全部友方部将共享。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14/14，嗜血：友方部将获得+4/+4。嗜血效果全部友方部将共享。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每当对己方使用属性增强类神通时，额外释放一次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12/18，每当你对己方使用属性增强类神通时，额外释放两次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残念：召唤1个地府蜘蛛。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6/4，残念：召唤2个地府蜘蛛。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/4，狂怒，嗜血：获得+2/+2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6/8，相邻部将获得：嗜血：获得+2攻击力。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1249,7 +1234,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1274,6 +1259,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1290,7 +1281,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1376,6 +1367,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1759,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{680D7D93-5AE3-4DC8-9319-D55788C423FC}">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1770,62 +1764,70 @@
     <col min="10" max="10" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="39" customHeight="1">
+    <row r="1" spans="1:18" ht="39" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>191</v>
+      <c r="J1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
-    </row>
-    <row r="2" spans="1:13" ht="40.5" customHeight="1">
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+    </row>
+    <row r="2" spans="1:18" ht="40.5" customHeight="1">
       <c r="B2" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="39" customHeight="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="39" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
@@ -1835,17 +1837,17 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13" ht="39" customHeight="1">
+    <row r="4" spans="1:18" ht="39" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
@@ -1855,17 +1857,17 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" ht="39" customHeight="1">
+    <row r="5" spans="1:18" ht="39" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -1875,17 +1877,17 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" ht="39" customHeight="1">
+    <row r="6" spans="1:18" ht="39" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -1895,17 +1897,17 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" ht="39" customHeight="1">
+    <row r="7" spans="1:18" ht="39" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -1915,17 +1917,17 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="1:13" ht="39" customHeight="1">
+    <row r="8" spans="1:18" ht="39" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>149</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -1935,17 +1937,17 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="1:13" ht="39" customHeight="1">
+    <row r="9" spans="1:18" ht="39" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -1955,17 +1957,17 @@
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="1:13" ht="39" customHeight="1">
+    <row r="10" spans="1:18" ht="39" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -1975,15 +1977,15 @@
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="1:13" ht="46.5" customHeight="1">
+    <row r="11" spans="1:18" ht="46.5" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -1993,7 +1995,7 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:18">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -2001,16 +2003,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
@@ -2019,7 +2021,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
     </row>
-    <row r="13" spans="1:13" ht="28.5">
+    <row r="13" spans="1:18" ht="28.5">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -2030,13 +2032,13 @@
         <v>1</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
@@ -2045,24 +2047,24 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:18">
       <c r="A14" s="8">
         <v>2</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -2071,24 +2073,24 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:18">
       <c r="A15" s="8">
         <v>2</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -2097,31 +2099,30 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="1:13" ht="57">
+    <row r="16" spans="1:18" ht="28.5">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G16" s="8"/>
-      <c r="H16" s="8" t="s">
-        <v>190</v>
-      </c>
       <c r="I16" s="8"/>
-      <c r="J16" s="10"/>
+      <c r="J16" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
@@ -2130,19 +2131,19 @@
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -2156,19 +2157,19 @@
         <v>3</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -2182,19 +2183,19 @@
         <v>3</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -2208,19 +2209,19 @@
         <v>4</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
@@ -2234,19 +2235,19 @@
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
@@ -2260,19 +2261,19 @@
         <v>4</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C22" s="20">
         <v>46057</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="28.5">
@@ -2280,19 +2281,19 @@
         <v>5</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -2306,19 +2307,19 @@
         <v>5</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -2332,19 +2333,19 @@
         <v>5</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
@@ -2358,25 +2359,25 @@
         <v>6</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
@@ -2386,19 +2387,19 @@
         <v>6</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
@@ -2412,19 +2413,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -2438,25 +2439,25 @@
         <v>6</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
@@ -2478,25 +2479,25 @@
     <row r="33" spans="1:13">
       <c r="D33" s="4"/>
       <c r="E33" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D34" s="4"/>
       <c r="G34" s="3"/>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E35" s="1"/>
     </row>
     <row r="36" spans="1:13" s="18" customFormat="1">
       <c r="A36" s="18" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="18" customFormat="1" ht="28.5" customHeight="1">
@@ -2504,27 +2505,27 @@
         <v>4</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="15"/>
       <c r="I37" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L37" s="19"/>
       <c r="M37" s="19"/>
@@ -2534,24 +2535,24 @@
         <v>5</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G38" s="15"/>
       <c r="H38" s="15"/>
       <c r="I38" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J38" s="17"/>
       <c r="L38" s="19"/>
@@ -2560,12 +2561,13 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E19F982C-7D94-4D1E-A263-41722DE2E3B1}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9" style="7"/>
@@ -2574,7 +2576,9 @@
     <col min="6" max="6" width="55.25" style="7" customWidth="1"/>
     <col min="7" max="7" width="29" style="7" customWidth="1"/>
     <col min="8" max="8" width="12.125" style="7" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="7"/>
+    <col min="9" max="10" width="9" style="7"/>
+    <col min="11" max="11" width="15.25" style="7" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39" customHeight="1">
@@ -2582,16 +2586,16 @@
         <v>7</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
@@ -2606,30 +2610,28 @@
         <v>12</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A2" s="26" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>218</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E2" s="25"/>
       <c r="F2" s="25" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="7"/>
@@ -2642,36 +2644,34 @@
         <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A4" s="25" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>220</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E4" s="25"/>
       <c r="F4" s="25" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="G4" s="25"/>
       <c r="H4" s="7"/>
@@ -2682,15 +2682,15 @@
     <row r="5" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A5" s="25"/>
       <c r="B5" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="25" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="G5" s="25"/>
       <c r="H5" s="7"/>
@@ -2699,26 +2699,26 @@
       <c r="K5" s="7"/>
     </row>
     <row r="6" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A6" s="25" t="s">
-        <v>217</v>
+      <c r="A6" s="25">
+        <v>1</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>282</v>
+        <v>14</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>136</v>
+        <v>212</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>300</v>
+        <v>214</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -2726,53 +2726,53 @@
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A7" s="25" t="s">
-        <v>217</v>
+      <c r="A7" s="25">
+        <v>1</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>222</v>
+        <v>13</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>128</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>283</v>
+        <v>216</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
+    <row r="8" spans="1:11" s="24" customFormat="1" ht="48" customHeight="1">
       <c r="A8" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>14</v>
+        <v>217</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>64</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>227</v>
+        <v>276</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -2781,52 +2781,50 @@
     </row>
     <row r="9" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A9" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>130</v>
+        <v>218</v>
+      </c>
+      <c r="C9" s="26">
+        <v>46055</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>205</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E9" s="25"/>
       <c r="F9" s="25" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>231</v>
+        <v>294</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" s="24" customFormat="1" ht="48" customHeight="1">
+    <row r="10" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A10" s="25">
         <v>2</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -2835,25 +2833,25 @@
     </row>
     <row r="11" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A11" s="25">
-        <v>2</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>235</v>
+        <v>3</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>206</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>237</v>
+        <v>292</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>238</v>
+        <v>293</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -2862,25 +2860,25 @@
     </row>
     <row r="12" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A12" s="25">
-        <v>2</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>239</v>
+        <v>3</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>270</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -2892,22 +2890,22 @@
         <v>3</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>130</v>
+        <v>268</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>271</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -2919,22 +2917,22 @@
         <v>3</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -2945,23 +2943,23 @@
       <c r="A15" s="25">
         <v>3</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>213</v>
+      <c r="B15" s="25" t="s">
+        <v>208</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -2973,22 +2971,22 @@
         <v>3</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>130</v>
+        <v>282</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>34</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>292</v>
+        <v>143</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>80</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -2999,23 +2997,21 @@
       <c r="A17" s="25">
         <v>3</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>216</v>
+      <c r="B17" s="27" t="s">
+        <v>267</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>207</v>
+        <v>16</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>251</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E17" s="25"/>
       <c r="F17" s="25" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -3026,47 +3022,49 @@
       <c r="A18" s="25">
         <v>3</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>17</v>
+      <c r="B18" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>249</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>220</v>
+        <v>279</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
+      <c r="K18" s="22" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="19" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A19" s="25">
         <v>3</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>290</v>
+        <v>225</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>15</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>257</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>285</v>
+        <v>143</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>259</v>
       </c>
       <c r="G19" s="25" t="s">
         <v>258</v>
@@ -3074,29 +3072,31 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
+      <c r="K19" s="22" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="20" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A20" s="25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>303</v>
+        <v>228</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>302</v>
+        <v>229</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -3108,22 +3108,22 @@
         <v>4</v>
       </c>
       <c r="B21" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="F21" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="C21" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>261</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>262</v>
-      </c>
       <c r="G21" s="25" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -3135,22 +3135,22 @@
         <v>4</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>194</v>
+        <v>61</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>304</v>
+        <v>233</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -3159,25 +3159,25 @@
     </row>
     <row r="23" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A23" s="25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>62</v>
+        <v>17</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -3189,22 +3189,22 @@
         <v>5</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -3216,22 +3216,22 @@
         <v>5</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>305</v>
+        <v>240</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -3240,25 +3240,25 @@
     </row>
     <row r="26" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
       <c r="A26" s="25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>274</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>69</v>
+        <v>47</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>192</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -3270,22 +3270,22 @@
         <v>6</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>195</v>
+        <v>21</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>243</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -3297,65 +3297,33 @@
         <v>6</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>279</v>
+        <v>19</v>
+      </c>
+      <c r="C28" s="28">
+        <v>46149</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A29" s="25">
-        <v>6</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="28">
-        <v>46149</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="G29" s="25" t="s">
-        <v>293</v>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="7">
-        <v>5</v>
-      </c>
-      <c r="F30" s="22"/>
-    </row>
     <row r="31" spans="1:11">
       <c r="A31" s="7">
         <v>5</v>
       </c>
+      <c r="F31" s="22"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="7">
@@ -3364,7 +3332,7 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -3374,6 +3342,11 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="7">
         <v>6</v>
       </c>
     </row>
@@ -3402,13 +3375,13 @@
         <v>7</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>9</v>
@@ -3423,11 +3396,11 @@
         <v>12</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J1" s="7"/>
       <c r="K1" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
@@ -3435,14 +3408,14 @@
     <row r="2" spans="1:13" ht="28.5">
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
@@ -3456,14 +3429,14 @@
     <row r="3" spans="1:13" ht="42.75">
       <c r="A3" s="8"/>
       <c r="B3" s="8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
@@ -3482,27 +3455,27 @@
         <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
@@ -3518,22 +3491,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" s="10"/>
       <c r="K5" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
@@ -3543,28 +3516,28 @@
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
@@ -3574,28 +3547,28 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
@@ -3605,26 +3578,26 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -3636,24 +3609,24 @@
         <v>2</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
@@ -3665,28 +3638,28 @@
         <v>3</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
@@ -3696,28 +3669,28 @@
         <v>3</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
@@ -3727,24 +3700,24 @@
         <v>3</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -3756,24 +3729,24 @@
         <v>4</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -3785,24 +3758,24 @@
         <v>4</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="F14" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -3814,24 +3787,24 @@
         <v>4</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
@@ -3843,28 +3816,28 @@
         <v>4</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J16" s="10"/>
       <c r="K16" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
@@ -3874,28 +3847,28 @@
         <v>5</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J17" s="10"/>
       <c r="K17" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
@@ -3905,24 +3878,24 @@
         <v>5</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
@@ -3934,24 +3907,24 @@
         <v>5</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
@@ -3963,24 +3936,24 @@
         <v>5</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
@@ -3992,24 +3965,24 @@
         <v>5</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -4021,24 +3994,24 @@
         <v>6</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
@@ -4050,24 +4023,24 @@
         <v>6</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E23" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
@@ -4090,7 +4063,7 @@
     <row r="25" spans="1:13">
       <c r="D25" s="4"/>
       <c r="E25" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:13">

--- a/工作-大圣牌/战棋/部将表.xlsx
+++ b/工作-大圣牌/战棋/部将表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\Notes\工作-大圣牌\战棋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2279A9D8-8AB6-4808-8941-31F85E4A67B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A459140E-85C9-463C-A332-B7F3736A9472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B49D72AB-5E3C-4C34-8961-13FDE0D82E2C}"/>
   </bookViews>
   <sheets>
     <sheet name="盘丝洞1-额外关键词" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="298">
   <si>
     <t>蜘蛛卵</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -813,10 +813,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>后援：随机获取1张蛛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>嗜血</t>
   </si>
   <si>
@@ -835,9 +831,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>小蜘蛛卵</t>
-  </si>
-  <si>
     <t>地府蜘蛛</t>
   </si>
   <si>
@@ -981,10 +974,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10/20，释放两次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1037,26 +1026,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>玄胎蛛卵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>碧青蛛卵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赤纹蛛卵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>嗜血：使其他盘丝洞部将获得+1/+1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>金壳蛛卵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4/2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1101,10 +1074,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>破碎蛛卵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4/4，登场：获得2张蛛丝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1154,6 +1123,46 @@
   </si>
   <si>
     <t>6/8，相邻部将获得：嗜血：获得+2攻击力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑色蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄色蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红色蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>·破碎蛛卵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/14，释放两次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合更使：随机获取1张蛛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阵容构筑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1281,7 +1290,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1342,9 +1351,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1366,11 +1372,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1777,8 +1783,8 @@
       <c r="D1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>205</v>
+      <c r="E1" s="22" t="s">
+        <v>204</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
@@ -2087,7 +2093,7 @@
         <v>134</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>200</v>
+        <v>296</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>161</v>
@@ -2178,24 +2184,24 @@
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" ht="42.75">
       <c r="A19" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -2204,24 +2210,24 @@
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="1:13" ht="42.75">
+    <row r="20" spans="1:13" ht="28.5">
       <c r="A20" s="8">
         <v>4</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
@@ -2230,70 +2236,70 @@
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="1:13" ht="28.5">
+    <row r="21" spans="1:13">
       <c r="A21" s="8">
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>190</v>
+        <v>197</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>130</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="10"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" spans="1:13">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="28.5">
       <c r="A22" s="8">
+        <v>5</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>4</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="C22" s="20">
-        <v>46057</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>199</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="10"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
     </row>
     <row r="23" spans="1:13" ht="28.5">
       <c r="A23" s="8">
         <v>5</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -2302,24 +2308,24 @@
       <c r="L23" s="7"/>
       <c r="M23" s="7"/>
     </row>
-    <row r="24" spans="1:13" ht="28.5">
+    <row r="24" spans="1:13">
       <c r="A24" s="8">
         <v>5</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -2328,12 +2334,12 @@
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" ht="28.5">
       <c r="A25" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>190</v>
@@ -2342,64 +2348,64 @@
         <v>134</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
-      <c r="J25" s="10"/>
+      <c r="J25" s="14" t="s">
+        <v>158</v>
+      </c>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
     </row>
-    <row r="26" spans="1:13" ht="28.5">
+    <row r="26" spans="1:13">
       <c r="A26" s="8">
         <v>6</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>190</v>
+        <v>71</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="14" t="s">
-        <v>158</v>
-      </c>
+      <c r="J26" s="10"/>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" ht="28.5">
       <c r="A27" s="8">
         <v>6</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
@@ -2408,59 +2414,33 @@
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
     </row>
-    <row r="28" spans="1:13" ht="28.5">
+    <row r="28" spans="1:13" ht="57">
       <c r="A28" s="8">
         <v>6</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="10"/>
+      <c r="J28" s="14" t="s">
+        <v>169</v>
+      </c>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:13" ht="57">
-      <c r="A29" s="8">
-        <v>6</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="8"/>
@@ -2567,11 +2547,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E19F982C-7D94-4D1E-A263-41722DE2E3B1}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9" style="7"/>
-    <col min="3" max="3" width="9" style="21"/>
+    <col min="3" max="3" width="9" style="20"/>
     <col min="4" max="5" width="11.875" style="7" customWidth="1"/>
     <col min="6" max="6" width="55.25" style="7" customWidth="1"/>
     <col min="7" max="7" width="29" style="7" customWidth="1"/>
@@ -2594,8 +2574,8 @@
       <c r="D1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>205</v>
+      <c r="E1" s="22" t="s">
+        <v>204</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
@@ -2616,24 +2596,24 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A2" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="B2" s="25" t="s">
+    <row r="2" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A2" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="D2" s="25" t="s">
+      <c r="C2" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="G2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="G2" s="24"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -2644,675 +2624,675 @@
         <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>255</v>
+        <v>251</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>252</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>143</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A4" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C4" s="26" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="G4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="G4" s="24"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A5" s="25"/>
+    <row r="5" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A5" s="24"/>
       <c r="B5" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="G5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" s="24"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A6" s="25">
+    <row r="6" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A6" s="24">
         <v>1</v>
       </c>
-      <c r="B6" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="C6" s="26" t="s">
+      <c r="B6" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="G6" s="24" t="s">
         <v>212</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>214</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A7" s="25">
+    <row r="7" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A7" s="24">
         <v>1</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>216</v>
+      <c r="E7" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>214</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" s="24" customFormat="1" ht="48" customHeight="1">
-      <c r="A8" s="25">
+    <row r="8" spans="1:11" s="23" customFormat="1" ht="48" customHeight="1">
+      <c r="A8" s="24">
         <v>2</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="C8" s="25" t="s">
+      <c r="B8" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>261</v>
+      <c r="E8" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>258</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A9" s="25">
+    <row r="9" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="25">
         <v>46055</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>294</v>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>286</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A10" s="25">
+    <row r="10" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A10" s="24">
         <v>2</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="C10" s="25" t="s">
+      <c r="B10" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E10" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>295</v>
+      <c r="E10" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>287</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A11" s="25">
+    <row r="11" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A11" s="24">
         <v>3</v>
       </c>
-      <c r="B11" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="C11" s="25" t="s">
+      <c r="B11" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>293</v>
+      <c r="E11" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>285</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A12" s="25">
+    <row r="12" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A12" s="24">
         <v>3</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="24" t="s">
         <v>270</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>277</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>221</v>
+      <c r="F12" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>219</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A13" s="25">
+    <row r="13" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A13" s="24">
         <v>3</v>
       </c>
-      <c r="B13" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="D13" s="25" t="s">
+      <c r="B13" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>269</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>272</v>
+      <c r="E13" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>265</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A14" s="25">
+    <row r="14" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A14" s="24">
         <v>3</v>
       </c>
-      <c r="B14" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="C14" s="25" t="s">
+      <c r="B14" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="25" t="s">
-        <v>277</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>222</v>
+      <c r="E14" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>220</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A15" s="25">
+    <row r="15" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A15" s="24">
         <v>3</v>
       </c>
-      <c r="B15" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" s="25" t="s">
+      <c r="B15" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="25" t="s">
-        <v>278</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>273</v>
+      <c r="E15" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>266</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A16" s="25">
+    <row r="16" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A16" s="24">
         <v>3</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>282</v>
-      </c>
-      <c r="C16" s="26" t="s">
+      <c r="B16" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="25" t="s">
-        <v>283</v>
+      <c r="G16" s="24" t="s">
+        <v>275</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A17" s="25">
+    <row r="17" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A17" s="24">
         <v>3</v>
       </c>
-      <c r="B17" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="C17" s="25" t="s">
+      <c r="B17" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>265</v>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>262</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A18" s="25">
+    <row r="18" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A18" s="24">
         <v>3</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="D18" s="25" t="s">
+      <c r="B18" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E18" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>274</v>
+      <c r="E18" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>267</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
-      <c r="K18" s="22" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A19" s="25">
+      <c r="K18" s="21" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A19" s="24">
         <v>3</v>
       </c>
-      <c r="B19" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="C19" s="25" t="s">
+      <c r="B19" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="F19" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>258</v>
+      <c r="F19" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>255</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
-      <c r="K19" s="22" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A20" s="25">
+      <c r="K19" s="21" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A20" s="24">
         <v>4</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="F20" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" s="25" t="s">
+      <c r="G20" s="24" t="s">
         <v>227</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>229</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A21" s="25">
+    <row r="21" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A21" s="24">
         <v>4</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E21" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>230</v>
+      <c r="E21" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>228</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A22" s="25">
+    <row r="22" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A22" s="24">
         <v>4</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="C22" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>246</v>
+      <c r="G22" s="24" t="s">
+        <v>244</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A23" s="25">
+    <row r="23" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A23" s="24">
         <v>5</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E23" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>284</v>
+      <c r="E23" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>276</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A24" s="25">
+    <row r="24" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A24" s="24">
         <v>5</v>
       </c>
-      <c r="B24" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="C24" s="25" t="s">
+      <c r="B24" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>286</v>
+      <c r="E24" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>278</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A25" s="25">
+    <row r="25" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A25" s="24">
         <v>5</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="F25" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="C25" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" s="25" t="s">
+      <c r="G25" s="24" t="s">
         <v>239</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>241</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A26" s="25">
+    <row r="26" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A26" s="24">
         <v>6</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E26" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>290</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>291</v>
+      <c r="E26" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>283</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A27" s="25">
+    <row r="27" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A27" s="24">
         <v>6</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="D27" s="25" t="s">
+      <c r="C27" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E27" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="G27" s="25" t="s">
-        <v>289</v>
+      <c r="E27" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>281</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:11" s="24" customFormat="1" ht="45.95" customHeight="1">
-      <c r="A28" s="25">
+    <row r="28" spans="1:11" s="23" customFormat="1" ht="45.95" customHeight="1">
+      <c r="A28" s="24">
         <v>6</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="28">
-        <v>46149</v>
-      </c>
-      <c r="D28" s="25" t="s">
+      <c r="C28" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="D28" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E28" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>257</v>
-      </c>
-      <c r="G28" s="25" t="s">
-        <v>252</v>
+      <c r="E28" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>295</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -3320,37 +3300,21 @@
       <c r="K28" s="7"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="7">
-        <v>5</v>
-      </c>
-      <c r="F31" s="22"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="7">
-        <v>6</v>
-      </c>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A33:E33"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
